--- a/artfynd/A 33941-2024 artfynd.xlsx
+++ b/artfynd/A 33941-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120435812</v>
+        <v>120435798</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>731532</v>
+        <v>731720</v>
       </c>
       <c r="R2" t="n">
-        <v>7182990</v>
+        <v>7182724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120435799</v>
+        <v>120435803</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>731700</v>
+        <v>731503</v>
       </c>
       <c r="R3" t="n">
-        <v>7182675</v>
+        <v>7182777</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120435809</v>
+        <v>120435806</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>731579</v>
+        <v>731551</v>
       </c>
       <c r="R4" t="n">
-        <v>7182970</v>
+        <v>7182852</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120435801</v>
+        <v>120435812</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>731651</v>
+        <v>731532</v>
       </c>
       <c r="R5" t="n">
-        <v>7182723</v>
+        <v>7182990</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120435792</v>
+        <v>120435801</v>
       </c>
       <c r="B6" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1095,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>731506</v>
+        <v>731651</v>
       </c>
       <c r="R6" t="n">
-        <v>7182944</v>
+        <v>7182723</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120435789</v>
+        <v>120435792</v>
       </c>
       <c r="B7" t="n">
-        <v>57320</v>
+        <v>96885</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>731552</v>
+        <v>731506</v>
       </c>
       <c r="R7" t="n">
-        <v>7182839</v>
+        <v>7182944</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120435803</v>
+        <v>120435799</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>731503</v>
+        <v>731700</v>
       </c>
       <c r="R9" t="n">
-        <v>7182777</v>
+        <v>7182675</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120435800</v>
+        <v>120435811</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>731658</v>
+        <v>731527</v>
       </c>
       <c r="R10" t="n">
-        <v>7182708</v>
+        <v>7182986</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,10 +1593,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120435790</v>
+        <v>120435807</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1609,21 +1609,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>731688</v>
+        <v>731619</v>
       </c>
       <c r="R11" t="n">
-        <v>7182713</v>
+        <v>7182915</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1695,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120435806</v>
+        <v>120435805</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1735,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>731551</v>
+        <v>731553</v>
       </c>
       <c r="R12" t="n">
-        <v>7182852</v>
+        <v>7182817</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1797,7 +1797,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120435798</v>
+        <v>120435800</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1837,10 +1837,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>731720</v>
+        <v>731658</v>
       </c>
       <c r="R13" t="n">
-        <v>7182724</v>
+        <v>7182708</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1899,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120435802</v>
+        <v>120435790</v>
       </c>
       <c r="B14" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1915,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1939,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>731547</v>
+        <v>731688</v>
       </c>
       <c r="R14" t="n">
-        <v>7182760</v>
+        <v>7182713</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2001,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120435805</v>
+        <v>120435802</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2041,10 +2041,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>731553</v>
+        <v>731547</v>
       </c>
       <c r="R15" t="n">
-        <v>7182817</v>
+        <v>7182760</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120435811</v>
+        <v>120435789</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2119,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2143,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>731527</v>
+        <v>731552</v>
       </c>
       <c r="R16" t="n">
-        <v>7182986</v>
+        <v>7182839</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2205,10 +2205,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120435808</v>
+        <v>120435795</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2221,21 +2221,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2245,10 +2245,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>731609</v>
+        <v>731577</v>
       </c>
       <c r="R17" t="n">
-        <v>7182931</v>
+        <v>7182973</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2281,11 +2281,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>med apotecier</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2312,7 +2307,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120435807</v>
+        <v>120435808</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2352,10 +2347,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>731619</v>
+        <v>731609</v>
       </c>
       <c r="R18" t="n">
-        <v>7182915</v>
+        <v>7182931</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2388,6 +2383,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>med apotecier</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120435795</v>
+        <v>120435809</v>
       </c>
       <c r="B19" t="n">
-        <v>90598</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5432</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>731577</v>
+        <v>731579</v>
       </c>
       <c r="R19" t="n">
-        <v>7182973</v>
+        <v>7182970</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 33941-2024 artfynd.xlsx
+++ b/artfynd/A 33941-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120435798</v>
+        <v>120435806</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>731720</v>
+        <v>731551</v>
       </c>
       <c r="R2" t="n">
-        <v>7182724</v>
+        <v>7182852</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120435803</v>
+        <v>120435807</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>731503</v>
+        <v>731619</v>
       </c>
       <c r="R3" t="n">
-        <v>7182777</v>
+        <v>7182915</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120435806</v>
+        <v>120435789</v>
       </c>
       <c r="B4" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>731551</v>
+        <v>731552</v>
       </c>
       <c r="R4" t="n">
-        <v>7182852</v>
+        <v>7182839</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120435792</v>
+        <v>120435800</v>
       </c>
       <c r="B7" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1197,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>731506</v>
+        <v>731658</v>
       </c>
       <c r="R7" t="n">
-        <v>7182944</v>
+        <v>7182708</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120435804</v>
+        <v>120435803</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>731549</v>
+        <v>731503</v>
       </c>
       <c r="R8" t="n">
-        <v>7182812</v>
+        <v>7182777</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1389,7 +1389,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120435799</v>
+        <v>120435809</v>
       </c>
       <c r="B9" t="n">
         <v>78542</v>
@@ -1429,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>731700</v>
+        <v>731579</v>
       </c>
       <c r="R9" t="n">
-        <v>7182675</v>
+        <v>7182970</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1491,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120435811</v>
+        <v>120435798</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1531,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>731527</v>
+        <v>731720</v>
       </c>
       <c r="R10" t="n">
-        <v>7182986</v>
+        <v>7182724</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120435807</v>
+        <v>120435808</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1633,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>731619</v>
+        <v>731609</v>
       </c>
       <c r="R11" t="n">
-        <v>7182915</v>
+        <v>7182931</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,6 +1669,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>med apotecier</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1797,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120435800</v>
+        <v>120435792</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1809,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1837,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>731658</v>
+        <v>731506</v>
       </c>
       <c r="R13" t="n">
-        <v>7182708</v>
+        <v>7182944</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1899,10 +1904,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120435790</v>
+        <v>120435802</v>
       </c>
       <c r="B14" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -1915,21 +1920,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1939,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>731688</v>
+        <v>731547</v>
       </c>
       <c r="R14" t="n">
-        <v>7182713</v>
+        <v>7182760</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2001,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120435802</v>
+        <v>120435811</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2041,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>731547</v>
+        <v>731527</v>
       </c>
       <c r="R15" t="n">
-        <v>7182760</v>
+        <v>7182986</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2103,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120435789</v>
+        <v>120435804</v>
       </c>
       <c r="B16" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2119,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2143,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>731552</v>
+        <v>731549</v>
       </c>
       <c r="R16" t="n">
-        <v>7182839</v>
+        <v>7182812</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2307,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120435808</v>
+        <v>120435799</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2347,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>731609</v>
+        <v>731700</v>
       </c>
       <c r="R18" t="n">
-        <v>7182931</v>
+        <v>7182675</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2383,11 +2388,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>med apotecier</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120435809</v>
+        <v>120435790</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>731579</v>
+        <v>731688</v>
       </c>
       <c r="R19" t="n">
-        <v>7182970</v>
+        <v>7182713</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 33941-2024 artfynd.xlsx
+++ b/artfynd/A 33941-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120435806</v>
+        <v>120435811</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>731551</v>
+        <v>731527</v>
       </c>
       <c r="R2" t="n">
-        <v>7182852</v>
+        <v>7182986</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120435789</v>
+        <v>120435805</v>
       </c>
       <c r="B4" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>731552</v>
+        <v>731553</v>
       </c>
       <c r="R4" t="n">
-        <v>7182839</v>
+        <v>7182817</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120435812</v>
+        <v>120435809</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>731532</v>
+        <v>731579</v>
       </c>
       <c r="R5" t="n">
-        <v>7182990</v>
+        <v>7182970</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120435801</v>
+        <v>120435806</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>731651</v>
+        <v>731551</v>
       </c>
       <c r="R6" t="n">
-        <v>7182723</v>
+        <v>7182852</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,7 +1185,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120435800</v>
+        <v>120435812</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>731658</v>
+        <v>731532</v>
       </c>
       <c r="R7" t="n">
-        <v>7182708</v>
+        <v>7182990</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,7 +1287,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120435803</v>
+        <v>120435808</v>
       </c>
       <c r="B8" t="n">
         <v>78542</v>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>731503</v>
+        <v>731609</v>
       </c>
       <c r="R8" t="n">
-        <v>7182777</v>
+        <v>7182931</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,6 +1363,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>med apotecier</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1389,10 +1394,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120435809</v>
+        <v>120435792</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1401,25 +1406,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1429,10 +1434,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>731579</v>
+        <v>731506</v>
       </c>
       <c r="R9" t="n">
-        <v>7182970</v>
+        <v>7182944</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1491,7 +1496,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120435798</v>
+        <v>120435801</v>
       </c>
       <c r="B10" t="n">
         <v>78542</v>
@@ -1531,10 +1536,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>731720</v>
+        <v>731651</v>
       </c>
       <c r="R10" t="n">
-        <v>7182724</v>
+        <v>7182723</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1593,7 +1598,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120435808</v>
+        <v>120435800</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1633,10 +1638,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>731609</v>
+        <v>731658</v>
       </c>
       <c r="R11" t="n">
-        <v>7182931</v>
+        <v>7182708</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1669,11 +1674,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>med apotecier</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1700,7 +1700,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120435805</v>
+        <v>120435798</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1740,10 +1740,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>731553</v>
+        <v>731720</v>
       </c>
       <c r="R12" t="n">
-        <v>7182817</v>
+        <v>7182724</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1802,10 +1802,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120435792</v>
+        <v>120435803</v>
       </c>
       <c r="B13" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1814,25 +1814,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>731506</v>
+        <v>731503</v>
       </c>
       <c r="R13" t="n">
-        <v>7182944</v>
+        <v>7182777</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120435802</v>
+        <v>120435804</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>731547</v>
+        <v>731549</v>
       </c>
       <c r="R14" t="n">
-        <v>7182760</v>
+        <v>7182812</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120435811</v>
+        <v>120435799</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>731527</v>
+        <v>731700</v>
       </c>
       <c r="R15" t="n">
-        <v>7182986</v>
+        <v>7182675</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120435804</v>
+        <v>120435790</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>731549</v>
+        <v>731688</v>
       </c>
       <c r="R16" t="n">
-        <v>7182812</v>
+        <v>7182713</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2312,7 +2312,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120435799</v>
+        <v>120435802</v>
       </c>
       <c r="B18" t="n">
         <v>78542</v>
@@ -2352,10 +2352,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>731700</v>
+        <v>731547</v>
       </c>
       <c r="R18" t="n">
-        <v>7182675</v>
+        <v>7182760</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120435790</v>
+        <v>120435789</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>731688</v>
+        <v>731552</v>
       </c>
       <c r="R19" t="n">
-        <v>7182713</v>
+        <v>7182839</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 33941-2024 artfynd.xlsx
+++ b/artfynd/A 33941-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120435811</v>
+        <v>120435798</v>
       </c>
       <c r="B2" t="n">
         <v>78542</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>731527</v>
+        <v>731720</v>
       </c>
       <c r="R2" t="n">
-        <v>7182986</v>
+        <v>7182724</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -777,7 +777,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120435807</v>
+        <v>120435805</v>
       </c>
       <c r="B3" t="n">
         <v>78542</v>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>731619</v>
+        <v>731553</v>
       </c>
       <c r="R3" t="n">
-        <v>7182915</v>
+        <v>7182817</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,7 +879,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120435805</v>
+        <v>120435812</v>
       </c>
       <c r="B4" t="n">
         <v>78542</v>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>731553</v>
+        <v>731532</v>
       </c>
       <c r="R4" t="n">
-        <v>7182817</v>
+        <v>7182990</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -981,7 +981,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120435809</v>
+        <v>120435800</v>
       </c>
       <c r="B5" t="n">
         <v>78542</v>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>731579</v>
+        <v>731658</v>
       </c>
       <c r="R5" t="n">
-        <v>7182970</v>
+        <v>7182708</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120435806</v>
+        <v>120435807</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>731551</v>
+        <v>731619</v>
       </c>
       <c r="R6" t="n">
-        <v>7182852</v>
+        <v>7182915</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120435812</v>
+        <v>120435795</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>90598</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>5432</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>731532</v>
+        <v>731577</v>
       </c>
       <c r="R7" t="n">
-        <v>7182990</v>
+        <v>7182973</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120435808</v>
+        <v>120435789</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>731609</v>
+        <v>731552</v>
       </c>
       <c r="R8" t="n">
-        <v>7182931</v>
+        <v>7182839</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1363,11 +1363,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2024-09-30</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>med apotecier</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1394,10 +1389,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120435792</v>
+        <v>120435806</v>
       </c>
       <c r="B9" t="n">
-        <v>96885</v>
+        <v>78542</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1406,25 +1401,25 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1434,10 +1429,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>731506</v>
+        <v>731551</v>
       </c>
       <c r="R9" t="n">
-        <v>7182944</v>
+        <v>7182852</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1496,10 +1491,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120435801</v>
+        <v>120435792</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>96885</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1508,25 +1503,25 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1536,10 +1531,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>731651</v>
+        <v>731506</v>
       </c>
       <c r="R10" t="n">
-        <v>7182723</v>
+        <v>7182944</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1598,7 +1593,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120435800</v>
+        <v>120435801</v>
       </c>
       <c r="B11" t="n">
         <v>78542</v>
@@ -1638,10 +1633,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>731658</v>
+        <v>731651</v>
       </c>
       <c r="R11" t="n">
-        <v>7182708</v>
+        <v>7182723</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1700,7 +1695,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120435798</v>
+        <v>120435808</v>
       </c>
       <c r="B12" t="n">
         <v>78542</v>
@@ -1740,10 +1735,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>731720</v>
+        <v>731609</v>
       </c>
       <c r="R12" t="n">
-        <v>7182724</v>
+        <v>7182931</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1776,6 +1771,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2024-09-30</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>med apotecier</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1802,7 +1802,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120435803</v>
+        <v>120435799</v>
       </c>
       <c r="B13" t="n">
         <v>78542</v>
@@ -1842,10 +1842,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>731503</v>
+        <v>731700</v>
       </c>
       <c r="R13" t="n">
-        <v>7182777</v>
+        <v>7182675</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1904,7 +1904,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120435804</v>
+        <v>120435811</v>
       </c>
       <c r="B14" t="n">
         <v>78542</v>
@@ -1944,10 +1944,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>731549</v>
+        <v>731527</v>
       </c>
       <c r="R14" t="n">
-        <v>7182812</v>
+        <v>7182986</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2006,7 +2006,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120435799</v>
+        <v>120435804</v>
       </c>
       <c r="B15" t="n">
         <v>78542</v>
@@ -2046,10 +2046,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>731700</v>
+        <v>731549</v>
       </c>
       <c r="R15" t="n">
-        <v>7182675</v>
+        <v>7182812</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120435790</v>
+        <v>120435803</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2124,21 +2124,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>731688</v>
+        <v>731503</v>
       </c>
       <c r="R16" t="n">
-        <v>7182713</v>
+        <v>7182777</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2210,10 +2210,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120435795</v>
+        <v>120435790</v>
       </c>
       <c r="B17" t="n">
-        <v>90598</v>
+        <v>57473</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2226,21 +2226,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5432</v>
+        <v>103021</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2250,10 +2250,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>731577</v>
+        <v>731688</v>
       </c>
       <c r="R17" t="n">
-        <v>7182973</v>
+        <v>7182713</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2414,10 +2414,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120435789</v>
+        <v>120435809</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2430,21 +2430,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2454,10 +2454,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>731552</v>
+        <v>731579</v>
       </c>
       <c r="R19" t="n">
-        <v>7182839</v>
+        <v>7182970</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>

--- a/artfynd/A 33941-2024 artfynd.xlsx
+++ b/artfynd/A 33941-2024 artfynd.xlsx
@@ -1185,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120435795</v>
+        <v>120435789</v>
       </c>
       <c r="B7" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1201,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>731577</v>
+        <v>731552</v>
       </c>
       <c r="R7" t="n">
-        <v>7182973</v>
+        <v>7182839</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1287,10 +1287,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120435789</v>
+        <v>120435795</v>
       </c>
       <c r="B8" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1303,21 +1303,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>731552</v>
+        <v>731577</v>
       </c>
       <c r="R8" t="n">
-        <v>7182839</v>
+        <v>7182973</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
